--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>10:53:34 AM</v>
+        <v>10:58:18 AM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>10:53:34 AM</v>
+        <v>10:58:18 AM</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>10:53:39 AM</v>
+        <v>10:58:23 AM</v>
       </c>
       <c r="H4">
-        <v>5161</v>
+        <v>5160</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>10:53:39 AM</v>
+        <v>10:58:23 AM</v>
       </c>
       <c r="H5">
-        <v>340</v>
+        <v>452</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>10:53:39 AM</v>
+        <v>10:58:24 AM</v>
       </c>
       <c r="H6">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:24 AM</v>
       </c>
       <c r="H7">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H8">
-        <v>321</v>
+        <v>772</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>10:53:40 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H17">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H18">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H19">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H20">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H37">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H38">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H39">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,10 +1561,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I40" t="str">
         <v>Longitude: LONGITUDE</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>10:53:41 AM</v>
+        <v>10:58:25 AM</v>
       </c>
       <c r="H41">
         <v>13</v>
       </c>
       <c r="I41" t="str">
-        <v>SIMATS Engineering Campus, Poonamallee, Chennai, Tamil Nadu, 602101, India</v>
+        <v>Orland Grassland Orange Primitive Trail, Orland Township, Cook County, Illinois, 60467, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H42">
-        <v>5153</v>
+        <v>5147</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>10:53:46 AM</v>
+        <v>10:58:31 AM</v>
       </c>
       <c r="H57">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H58">
-        <v>5154</v>
+        <v>5169</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H72">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H73">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>10:53:51 AM</v>
+        <v>10:58:36 AM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,14 +2577,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>10:54:01 AM</v>
+        <v>10:58:46 AM</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(text(), '9ca4') or contains(text(), 'dee5')])
-Wait timed out after 10077ms</v>
+Wait timed out after 10046ms</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>10:54:11 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10069ms</v>
+Wait timed out after 10099ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H77">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:56 AM</v>
       </c>
       <c r="H87">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:57 AM</v>
       </c>
       <c r="H88">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,10 +2985,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>10:54:12 AM</v>
+        <v>10:58:57 AM</v>
       </c>
       <c r="H89">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:57 AM</v>
       </c>
       <c r="H90">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H91">
-        <v>398</v>
+        <v>544</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>10:54:13 AM</v>
+        <v>10:58:58 AM</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>10:58:18 AM</v>
+        <v>10:59:41 AM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>10:58:18 AM</v>
+        <v>10:59:41 AM</v>
       </c>
       <c r="H3">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>10:58:23 AM</v>
+        <v>10:59:47 AM</v>
       </c>
       <c r="H4">
-        <v>5160</v>
+        <v>5191</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>10:58:23 AM</v>
+        <v>10:59:47 AM</v>
       </c>
       <c r="H5">
-        <v>452</v>
+        <v>360</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>10:58:24 AM</v>
+        <v>10:59:47 AM</v>
       </c>
       <c r="H6">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10:58:24 AM</v>
+        <v>10:59:47 AM</v>
       </c>
       <c r="H7">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H8">
-        <v>772</v>
+        <v>443</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H17">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:48 AM</v>
       </c>
       <c r="H19">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H20">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H37">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H38">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H39">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,10 +1561,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H40">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I40" t="str">
         <v>Longitude: LONGITUDE</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>10:58:25 AM</v>
+        <v>10:59:49 AM</v>
       </c>
       <c r="H41">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I41" t="str">
-        <v>Orland Grassland Orange Primitive Trail, Orland Township, Cook County, Illinois, 60467, United States</v>
+        <v>23219, Evergreen Mills Road, Brambleton, Loudoun County, Virginia, 20146, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H42">
-        <v>5147</v>
+        <v>5184</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>10:58:31 AM</v>
+        <v>10:59:54 AM</v>
       </c>
       <c r="H57">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H58">
-        <v>5169</v>
+        <v>5161</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H72">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H73">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>10:58:36 AM</v>
+        <v>10:59:59 AM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,14 +2577,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>10:58:46 AM</v>
+        <v>11:00:09 AM</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(text(), '9ca4') or contains(text(), 'dee5')])
-Wait timed out after 10046ms</v>
+Wait timed out after 10017ms</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:19 AM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10099ms</v>
+Wait timed out after 10069ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H77">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,7 +2927,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>10:58:56 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H87">
         <v>67</v>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>10:58:57 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H88">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,10 +2985,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>10:58:57 AM</v>
+        <v>11:00:20 AM</v>
       </c>
       <c r="H89">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>10:58:57 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H90">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H91">
-        <v>544</v>
+        <v>441</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>10:58:58 AM</v>
+        <v>11:00:21 AM</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>10:59:41 AM</v>
+        <v>11:00:51 AM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>10:59:41 AM</v>
+        <v>11:00:51 AM</v>
       </c>
       <c r="H3">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>10:59:47 AM</v>
+        <v>11:00:56 AM</v>
       </c>
       <c r="H4">
-        <v>5191</v>
+        <v>5168</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>10:59:47 AM</v>
+        <v>11:00:56 AM</v>
       </c>
       <c r="H5">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>10:59:47 AM</v>
+        <v>11:00:56 AM</v>
       </c>
       <c r="H6">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>10:59:47 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H7">
-        <v>290</v>
+        <v>347</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H8">
-        <v>443</v>
+        <v>326</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H17">
-        <v>500</v>
+        <v>332</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,7 +923,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:57 AM</v>
       </c>
       <c r="H18">
         <v>18</v>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>10:59:48 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H19">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H20">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H37">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H38">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H39">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,10 +1561,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I40" t="str">
         <v>Longitude: LONGITUDE</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>10:59:49 AM</v>
+        <v>11:00:58 AM</v>
       </c>
       <c r="H41">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I41" t="str">
-        <v>23219, Evergreen Mills Road, Brambleton, Loudoun County, Virginia, 20146, United States</v>
+        <v>Aviemore Lane, Johnston County, North Carolina, 27561, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H42">
-        <v>5184</v>
+        <v>5144</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>10:59:54 AM</v>
+        <v>11:01:03 AM</v>
       </c>
       <c r="H57">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H58">
-        <v>5161</v>
+        <v>5165</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,7 +2489,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H72">
         <v>61</v>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H73">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>10:59:59 AM</v>
+        <v>11:01:08 AM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,14 +2577,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:00:09 AM</v>
+        <v>11:01:18 AM</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(text(), '9ca4') or contains(text(), 'dee5')])
-Wait timed out after 10017ms</v>
+Wait timed out after 10075ms</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:00:19 AM</v>
+        <v>11:01:28 AM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10069ms</v>
+Wait timed out after 10079ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H77">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H87">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H88">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,10 +2985,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:00:20 AM</v>
+        <v>11:01:29 AM</v>
       </c>
       <c r="H89">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H90">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H91">
-        <v>441</v>
+        <v>409</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:00:21 AM</v>
+        <v>11:01:30 AM</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:00:51 AM</v>
+        <v>11:01:55 AM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:00:51 AM</v>
+        <v>11:01:55 AM</v>
       </c>
       <c r="H3">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:00:56 AM</v>
+        <v>11:02:00 AM</v>
       </c>
       <c r="H4">
-        <v>5168</v>
+        <v>5158</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:00:56 AM</v>
+        <v>11:02:00 AM</v>
       </c>
       <c r="H5">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:00:56 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H6">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H7">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H8">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:01 AM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H17">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:00:57 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H19">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H20">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H37">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H38">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H39">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,7 +1561,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H40">
         <v>14</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:00:58 AM</v>
+        <v>11:02:02 AM</v>
       </c>
       <c r="H41">
         <v>13</v>
       </c>
       <c r="I41" t="str">
-        <v>Aviemore Lane, Johnston County, North Carolina, 27561, United States</v>
+        <v>1315, East Willetta Street, North Garfield, Central City, Phoenix, Maricopa County, Arizona, 85006, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H42">
-        <v>5144</v>
+        <v>5142</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:01:03 AM</v>
+        <v>11:02:07 AM</v>
       </c>
       <c r="H57">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H58">
-        <v>5165</v>
+        <v>5153</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H72">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H73">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:01:08 AM</v>
+        <v>11:02:12 AM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:01:18 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:01:28 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10079ms</v>
+Wait timed out after 10078ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H77">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H87">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:33 AM</v>
       </c>
       <c r="H88">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,10 +2985,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:01:29 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H89">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H90">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H91">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:01:30 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:01:55 AM</v>
+        <v>11:02:17 AM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:01:55 AM</v>
+        <v>11:02:17 AM</v>
       </c>
       <c r="H3">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:02:00 AM</v>
+        <v>11:02:22 AM</v>
       </c>
       <c r="H4">
-        <v>5158</v>
+        <v>5162</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:02:00 AM</v>
+        <v>11:02:22 AM</v>
       </c>
       <c r="H5">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H6">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H7">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H8">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:02:01 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:23 AM</v>
       </c>
       <c r="H17">
-        <v>342</v>
+        <v>213</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H19">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H20">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H37">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H38">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H39">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,10 +1561,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" t="str">
         <v>Longitude: LONGITUDE</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:02:02 AM</v>
+        <v>11:02:24 AM</v>
       </c>
       <c r="H41">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I41" t="str">
-        <v>1315, East Willetta Street, North Garfield, Central City, Phoenix, Maricopa County, Arizona, 85006, United States</v>
+        <v>Crest Hill Road, Keysville, Flint Hill, Rappahannock County, Virginia, 22627, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H42">
-        <v>5142</v>
+        <v>5143</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:02:07 AM</v>
+        <v>11:02:29 AM</v>
       </c>
       <c r="H57">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H58">
-        <v>5153</v>
+        <v>5151</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H72">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H73">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:02:12 AM</v>
+        <v>11:02:34 AM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:02:23 AM</v>
+        <v>11:02:44 AM</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:54 AM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10078ms</v>
+Wait timed out after 10077ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H77">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H87">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:02:33 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H88">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,7 +2985,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:55 AM</v>
       </c>
       <c r="H89">
         <v>275</v>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H90">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H91">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:02:34 AM</v>
+        <v>11:02:56 AM</v>
       </c>
       <c r="H106">
         <v>1</v>

--- a/test-analysis-report.xlsx
+++ b/test-analysis-report.xlsx
@@ -459,7 +459,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G2" t="str">
-        <v>11:02:17 AM</v>
+        <v>5:32:33 PM</v>
       </c>
       <c r="H2">
         <v>5</v>
@@ -488,10 +488,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G3" t="str">
-        <v>11:02:17 AM</v>
+        <v>5:32:33 PM</v>
       </c>
       <c r="H3">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -517,10 +517,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G4" t="str">
-        <v>11:02:22 AM</v>
+        <v>5:32:38 PM</v>
       </c>
       <c r="H4">
-        <v>5162</v>
+        <v>5179</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -546,10 +546,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G5" t="str">
-        <v>11:02:22 AM</v>
+        <v>5:32:38 PM</v>
       </c>
       <c r="H5">
-        <v>282</v>
+        <v>314</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -575,10 +575,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G6" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H6">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -604,10 +604,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G7" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H7">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -633,10 +633,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G8" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H8">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -662,7 +662,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G9" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G10" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -720,7 +720,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G11" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -749,7 +749,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G12" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -778,7 +778,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G13" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -807,7 +807,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G14" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -836,7 +836,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G15" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -865,7 +865,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G16" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:39 PM</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -894,10 +894,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G17" t="str">
-        <v>11:02:23 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H17">
-        <v>213</v>
+        <v>521</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -923,10 +923,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G18" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H18">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -952,10 +952,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G19" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H19">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -981,10 +981,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G20" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H20">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1010,7 +1010,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G21" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G22" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G23" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1097,7 +1097,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G24" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1126,7 +1126,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G25" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G26" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1184,7 +1184,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G27" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1213,7 +1213,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G28" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1242,7 +1242,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G29" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1271,7 +1271,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G30" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1300,7 +1300,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G31" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1329,7 +1329,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G32" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -1358,7 +1358,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G33" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1387,7 +1387,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G34" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -1416,7 +1416,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G35" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1445,7 +1445,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G36" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1474,10 +1474,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G37" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1503,10 +1503,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G38" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G39" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H39">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I39" t="str">
         <v>Latitude: LATITUDE</v>
@@ -1561,10 +1561,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G40" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I40" t="str">
         <v>Longitude: LONGITUDE</v>
@@ -1590,13 +1590,13 @@
         <v>6/14/2026</v>
       </c>
       <c r="G41" t="str">
-        <v>11:02:24 AM</v>
+        <v>5:32:40 PM</v>
       </c>
       <c r="H41">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I41" t="str">
-        <v>Crest Hill Road, Keysville, Flint Hill, Rappahannock County, Virginia, 22627, United States</v>
+        <v>Middle Street, Washington, Rappahannock County, Virginia, 22747, United States</v>
       </c>
     </row>
     <row r="42">
@@ -1619,10 +1619,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G42" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H42">
-        <v>5143</v>
+        <v>5142</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1648,7 +1648,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G43" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -1677,7 +1677,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G44" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -1706,7 +1706,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G45" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -1735,7 +1735,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G46" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G47" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1793,7 +1793,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G48" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -1822,7 +1822,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G49" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -1851,7 +1851,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G50" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -1880,7 +1880,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G51" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -1909,7 +1909,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G52" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -1938,7 +1938,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G53" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -1967,7 +1967,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G54" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -1996,7 +1996,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G55" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2025,7 +2025,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G56" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2054,10 +2054,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G57" t="str">
-        <v>11:02:29 AM</v>
+        <v>5:32:45 PM</v>
       </c>
       <c r="H57">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2083,10 +2083,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G58" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H58">
-        <v>5151</v>
+        <v>5150</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2112,7 +2112,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G59" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2141,7 +2141,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G60" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G61" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G62" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2228,7 +2228,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G63" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2257,7 +2257,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G64" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2286,7 +2286,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G65" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -2315,7 +2315,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G66" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2344,7 +2344,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G67" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G68" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2402,7 +2402,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G69" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2431,7 +2431,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G70" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G71" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2489,10 +2489,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G72" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:50 PM</v>
       </c>
       <c r="H72">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2518,10 +2518,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G73" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:51 PM</v>
       </c>
       <c r="H73">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I73" t="str">
         <v>Found 0 items</v>
@@ -2547,7 +2547,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G74" t="str">
-        <v>11:02:34 AM</v>
+        <v>5:32:51 PM</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -2577,14 +2577,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G75" t="str">
-        <v>11:02:44 AM</v>
+        <v>5:33:01 PM</v>
       </c>
       <c r="H75">
         <v>0</v>
       </c>
       <c r="I75" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //div[contains(text(), '9ca4') or contains(text(), 'dee5')])
-Wait timed out after 10075ms</v>
+Wait timed out after 10027ms</v>
       </c>
     </row>
     <row r="76" xml:space="preserve">
@@ -2607,14 +2607,14 @@
         <v>6/14/2026</v>
       </c>
       <c r="G76" t="str">
-        <v>11:02:54 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H76">
         <v>0</v>
       </c>
       <c r="I76" t="str" xml:space="preserve">
         <v xml:space="preserve">Waiting for element to be located By(xpath, //span[contains(@class, 'VERIFIED') or contains(text(), 'VERIFIED') or contains(text(), 'TAMPERED')])
-Wait timed out after 10077ms</v>
+Wait timed out after 10088ms</v>
       </c>
     </row>
     <row r="77">
@@ -2637,10 +2637,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G77" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H77">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -2666,7 +2666,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G78" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -2695,7 +2695,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G79" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -2724,7 +2724,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G80" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -2753,7 +2753,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G81" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G82" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -2811,7 +2811,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G83" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G84" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -2869,7 +2869,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G85" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -2898,7 +2898,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G86" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -2927,10 +2927,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G87" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H87">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -2956,10 +2956,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G88" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:11 PM</v>
       </c>
       <c r="H88">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -2985,10 +2985,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G89" t="str">
-        <v>11:02:55 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H89">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3014,10 +3014,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G90" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H90">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3043,10 +3043,10 @@
         <v>6/14/2026</v>
       </c>
       <c r="G91" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H91">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3072,7 +3072,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G92" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G93" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3130,7 +3130,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G94" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3159,7 +3159,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G95" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3188,7 +3188,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G96" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3217,7 +3217,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G97" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3246,7 +3246,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G98" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3275,7 +3275,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G99" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G100" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G101" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G102" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G103" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G104" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -3449,7 +3449,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G105" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -3478,7 +3478,7 @@
         <v>6/14/2026</v>
       </c>
       <c r="G106" t="str">
-        <v>11:02:56 AM</v>
+        <v>5:33:12 PM</v>
       </c>
       <c r="H106">
         <v>1</v>
